--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -718,8 +718,8 @@
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>21100</v>
       </c>
       <c r="E8" s="3">
         <v>11400</v>
@@ -750,8 +750,8 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>3400</v>
       </c>
       <c r="E9" s="3">
         <v>1000</v>
@@ -782,8 +782,8 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>17700</v>
       </c>
       <c r="E10" s="3">
         <v>10400</v>
@@ -924,8 +924,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>1700</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -967,8 +967,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>14800</v>
       </c>
       <c r="E17" s="3">
         <v>3000</v>
@@ -999,8 +999,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>6300</v>
       </c>
       <c r="E18" s="3">
         <v>8400</v>
@@ -1045,8 +1045,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-3500</v>
       </c>
       <c r="E20" s="3">
         <v>-500</v>
@@ -1077,8 +1077,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>4500</v>
       </c>
       <c r="E21" s="3">
         <v>7900</v>
@@ -1237,8 +1237,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>1100</v>
       </c>
       <c r="E26" s="3">
         <v>6700</v>
@@ -1269,8 +1269,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>900</v>
       </c>
       <c r="E27" s="3">
         <v>6800</v>
@@ -1429,8 +1429,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>3500</v>
       </c>
       <c r="E32" s="3">
         <v>500</v>
@@ -1461,8 +1461,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>900</v>
       </c>
       <c r="E33" s="3">
         <v>6800</v>
@@ -1525,8 +1525,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>900</v>
       </c>
       <c r="E35" s="3">
         <v>6800</v>
@@ -1687,7 +1687,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E43" s="3">
         <v>10800</v>
@@ -1815,7 +1815,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>90400</v>
+        <v>91800</v>
       </c>
       <c r="E47" s="3">
         <v>69200</v>
@@ -1974,8 +1974,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
         <v>2300</v>
@@ -2163,7 +2163,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="E59" s="3">
         <v>13500</v>
@@ -2227,7 +2227,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>118800</v>
       </c>
       <c r="E61" s="3">
         <v>91200</v>
@@ -2560,8 +2560,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-28500</v>
       </c>
       <c r="E72" s="3">
         <v>-29400</v>
@@ -2688,8 +2688,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>165800</v>
       </c>
       <c r="E76" s="3">
         <v>160100</v>
@@ -2789,8 +2789,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>900</v>
       </c>
       <c r="E81" s="3">
         <v>6800</v>
@@ -2835,8 +2835,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1700</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -3169,8 +3169,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>9600</v>
       </c>
       <c r="E94" s="3">
         <v>-6100</v>

--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -656,161 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F8" s="3">
         <v>21100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>11400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>10300</v>
       </c>
-      <c r="G8" s="3">
-        <v>44700</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8400</v>
-      </c>
       <c r="I8" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K8" s="3">
         <v>9900</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F9" s="3">
         <v>3400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>700</v>
-      </c>
       <c r="I9" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F10" s="3">
         <v>17700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>10400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>9800</v>
       </c>
-      <c r="G10" s="3">
-        <v>38500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>7700</v>
-      </c>
       <c r="I10" s="3">
+        <v>12500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K10" s="3">
         <v>8500</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +847,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +881,14 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,40 +919,52 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -928,10 +972,10 @@
         <v>1700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -942,17 +986,23 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +1012,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F17" s="3">
         <v>14800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3100</v>
-      </c>
       <c r="I17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>800</v>
+      </c>
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>6300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
       </c>
-      <c r="G18" s="3">
-        <v>33700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>5300</v>
-      </c>
       <c r="I18" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K18" s="3">
         <v>7200</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,72 +1104,86 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F21" s="3">
         <v>4500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>7000</v>
       </c>
-      <c r="G21" s="3">
-        <v>33300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>5200</v>
-      </c>
       <c r="I21" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K21" s="3">
         <v>7000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,78 +1208,96 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F23" s="3">
         <v>2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>7900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>7000</v>
       </c>
-      <c r="G23" s="3">
-        <v>33300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>5200</v>
-      </c>
       <c r="I23" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K23" s="3">
         <v>7000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>400</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1328,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>7600</v>
       </c>
-      <c r="G26" s="3">
-        <v>32400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>5100</v>
-      </c>
       <c r="I26" s="3">
+        <v>10100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K26" s="3">
         <v>6800</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>8100</v>
       </c>
-      <c r="G27" s="3">
-        <v>31700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>4700</v>
-      </c>
       <c r="I27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K27" s="3">
         <v>6800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1442,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,14 +1474,20 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1518,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1556,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
-        <v>400</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>8100</v>
       </c>
-      <c r="G33" s="3">
-        <v>31700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>4700</v>
-      </c>
       <c r="I33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K33" s="3">
         <v>6800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1670,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>8100</v>
       </c>
-      <c r="G35" s="3">
-        <v>31700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>4700</v>
-      </c>
       <c r="I35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K35" s="3">
         <v>6800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1771,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,26 +1787,28 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F41" s="3">
         <v>36600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1649,58 +1821,70 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+        <v>2300</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>10800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,8 +1897,14 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1739,32 +1929,38 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,26 +1973,32 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>31800</v>
+      </c>
+      <c r="F46" s="3">
         <v>39500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>32200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>23900</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,26 +2011,32 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>126800</v>
+      </c>
+      <c r="F47" s="3">
         <v>91800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>69200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>65400</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,26 +2049,32 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1873,23 +2087,29 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>169900</v>
+      </c>
+      <c r="F49" s="3">
         <v>171500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>173200</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1905,8 +2125,14 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2163,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,26 +2201,32 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2001,8 +2239,14 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,26 +2277,32 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>331800</v>
+      </c>
+      <c r="F54" s="3">
         <v>304300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>277300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>90400</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2065,8 +2315,14 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2335,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,26 +2351,28 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15000</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,58 +2385,70 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+        <v>13000</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,26 +2461,32 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F60" s="3">
         <v>5500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>16700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2221,26 +2499,32 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>126800</v>
+      </c>
+      <c r="F61" s="3">
         <v>118800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>91200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>37400</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2253,26 +2537,32 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F62" s="3">
         <v>13900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,8 +2575,14 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2613,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2651,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,26 +2689,32 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>167900</v>
+      </c>
+      <c r="F66" s="3">
         <v>138500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>117200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>55200</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2413,8 +2727,14 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2747,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2781,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2819,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,14 +2851,20 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,26 +2895,32 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-29400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>33600</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,8 +2933,14 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2971,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3009,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,26 +3047,32 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>163900</v>
+      </c>
+      <c r="F76" s="3">
         <v>165800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>160100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>35300</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2715,8 +3085,14 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3123,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>8100</v>
       </c>
-      <c r="G81" s="3">
-        <v>31700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>4700</v>
-      </c>
       <c r="I81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K81" s="3">
         <v>6800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,8 +3224,10 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2839,10 +3235,10 @@
         <v>1700</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -2853,17 +3249,23 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3296,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3334,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3372,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3410,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3448,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-12800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-21000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-17400</v>
       </c>
-      <c r="G89" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-9000</v>
-      </c>
       <c r="I89" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K89" s="3">
         <v>4200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,19 +3506,21 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3100,8 +3540,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3578,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3616,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
         <v>9600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>1000</v>
-      </c>
       <c r="I94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3674,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3708,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3746,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3784,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3822,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F100" s="3">
         <v>19200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>27900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>8000</v>
       </c>
-      <c r="G100" s="3">
-        <v>23000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K100" s="3">
         <v>3900</v>
       </c>
-      <c r="I100" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3396,42 +3892,54 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F102" s="3">
         <v>16000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-10300</v>
       </c>
-      <c r="G102" s="3">
-        <v>30000</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-4000</v>
-      </c>
       <c r="I102" s="3">
+        <v>26200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K102" s="3">
         <v>6800</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -656,109 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E8" s="3">
         <v>21500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,75 +773,81 @@
         <v>2700</v>
       </c>
       <c r="E9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E10" s="3">
         <v>18800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,20 +942,23 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,25 +971,28 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="3">
         <v>1700</v>
@@ -978,7 +1001,7 @@
         <v>1700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -992,8 +1015,8 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1001,8 +1024,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1040,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E17" s="3">
         <v>19200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,84 +1139,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1214,90 +1254,99 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1480,14 +1541,17 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,84 +1629,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E32" s="3">
         <v>2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,29 +1875,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E41" s="3">
         <v>65400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,20 +1914,23 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2300</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1853,41 +1943,44 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,8 +1996,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1935,35 +2031,38 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,29 +2078,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E46" s="3">
         <v>74300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,29 +2119,32 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E47" s="3">
         <v>129800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>126800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>91800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>69200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2055,29 +2160,32 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>400</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
       </c>
       <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,26 +2201,29 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E49" s="3">
         <v>168300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>169900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>171500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>173200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2131,8 +2242,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,8 +2324,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2216,20 +2336,20 @@
         <v>1500</v>
       </c>
       <c r="E52" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F52" s="3">
         <v>1000</v>
       </c>
       <c r="G52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2365,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,29 +2406,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>483900</v>
+      </c>
+      <c r="E54" s="3">
         <v>376700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>331800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>304300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>277300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>90400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2447,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,29 +2483,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,20 +2522,23 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E58" s="3">
         <v>15600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13000</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2417,41 +2551,44 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,29 +2604,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E60" s="3">
         <v>23800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16700</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,29 +2645,32 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E61" s="3">
         <v>170200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>126800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>118800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>91200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2543,29 +2686,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E62" s="3">
         <v>17400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,8 +2727,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,29 +2850,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>227100</v>
+      </c>
+      <c r="E66" s="3">
         <v>211600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>167900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>138500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2891,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2857,14 +3025,17 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,29 +3072,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-36100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-34700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,8 +3113,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,29 +3236,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E76" s="3">
         <v>165100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>163900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>165800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>160100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35300</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3277,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,13 +3424,14 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E83" s="3">
         <v>1700</v>
@@ -3241,7 +3440,7 @@
         <v>1700</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -3255,8 +3454,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3264,8 +3463,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="E89" s="3">
         <v>2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,22 +3728,23 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3546,8 +3767,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>9600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E100" s="3">
         <v>37500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3898,48 +4147,54 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E102" s="3">
         <v>39800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -656,198 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E8" s="3">
         <v>29100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2700</v>
+        <v>2200</v>
       </c>
       <c r="E9" s="3">
         <v>2700</v>
       </c>
       <c r="F9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>26400</v>
+        <v>26000</v>
       </c>
       <c r="E10" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F10" s="3">
         <v>18800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22000</v>
       </c>
-      <c r="G10" s="3">
-        <v>17700</v>
-      </c>
       <c r="H10" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I10" s="3">
         <v>10400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,57 +962,63 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>700</v>
       </c>
       <c r="F14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1700</v>
       </c>
       <c r="F15" s="3">
         <v>1700</v>
@@ -1004,7 +1027,7 @@
         <v>1700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1018,8 +1041,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1067,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22300</v>
+        <v>21600</v>
       </c>
       <c r="E17" s="3">
-        <v>19200</v>
+        <v>21600</v>
       </c>
       <c r="F17" s="3">
-        <v>23800</v>
+        <v>17700</v>
       </c>
       <c r="G17" s="3">
-        <v>14800</v>
+        <v>20500</v>
       </c>
       <c r="H17" s="3">
-        <v>3000</v>
+        <v>16600</v>
       </c>
       <c r="I17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L17" s="3">
+        <v>800</v>
+      </c>
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="E18" s="3">
-        <v>2300</v>
+        <v>7500</v>
       </c>
       <c r="F18" s="3">
-        <v>-100</v>
+        <v>3800</v>
       </c>
       <c r="G18" s="3">
-        <v>6300</v>
+        <v>3200</v>
       </c>
       <c r="H18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J18" s="3">
         <v>8400</v>
       </c>
-      <c r="I18" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,113 +1173,120 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4400</v>
+        <v>8800</v>
       </c>
       <c r="E20" s="3">
-        <v>-2400</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>-7000</v>
+        <v>-900</v>
       </c>
       <c r="G20" s="3">
-        <v>-3500</v>
+        <v>3400</v>
       </c>
       <c r="H20" s="3">
-        <v>-500</v>
+        <v>900</v>
       </c>
       <c r="I20" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4200</v>
+        <v>-500</v>
       </c>
       <c r="E21" s="3">
-        <v>1600</v>
+        <v>8800</v>
       </c>
       <c r="F21" s="3">
-        <v>-5400</v>
+        <v>6400</v>
       </c>
       <c r="G21" s="3">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H21" s="3">
-        <v>7900</v>
+        <v>5300</v>
       </c>
       <c r="I21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>10700</v>
+      </c>
+      <c r="M21" s="3">
         <v>7000</v>
       </c>
-      <c r="J21" s="3">
-        <v>10400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>10700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>7000</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1257,96 +1297,105 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1435,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6800</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,14 +1605,17 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,90 +1699,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4400</v>
+        <v>-8800</v>
       </c>
       <c r="E32" s="3">
-        <v>2400</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>7000</v>
+        <v>900</v>
       </c>
       <c r="G32" s="3">
-        <v>3500</v>
+        <v>-3400</v>
       </c>
       <c r="H32" s="3">
-        <v>500</v>
+        <v>-900</v>
       </c>
       <c r="I32" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1831,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,32 +1962,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E41" s="3">
         <v>91300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>65400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,73 +2004,79 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
-        <v>3500</v>
-      </c>
       <c r="F43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,31 +2092,34 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2034,34 +2130,37 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2081,32 +2180,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E46" s="3">
         <v>101600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,31 +2224,34 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>211600</v>
+        <v>3000</v>
       </c>
       <c r="E47" s="3">
-        <v>129800</v>
+        <v>2900</v>
       </c>
       <c r="F47" s="3">
-        <v>126800</v>
+        <v>2900</v>
       </c>
       <c r="G47" s="3">
-        <v>91800</v>
+        <v>2900</v>
       </c>
       <c r="H47" s="3">
-        <v>69200</v>
+        <v>4100</v>
       </c>
       <c r="I47" s="3">
-        <v>65400</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>2900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2163,32 +2268,35 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
       </c>
       <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,31 +2312,34 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E49" s="3">
         <v>166300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>168300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>169900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>171500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>173200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,31 +2444,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1500</v>
+        <v>276000</v>
       </c>
       <c r="E52" s="3">
-        <v>1500</v>
+        <v>210200</v>
       </c>
       <c r="F52" s="3">
-        <v>1000</v>
+        <v>128400</v>
       </c>
       <c r="G52" s="3">
-        <v>1000</v>
+        <v>125000</v>
       </c>
       <c r="H52" s="3">
-        <v>2300</v>
+        <v>88700</v>
       </c>
       <c r="I52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>68700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>64000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2368,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,32 +2532,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>477300</v>
+      </c>
+      <c r="E54" s="3">
         <v>483900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>376700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>331800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>304300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>277300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,8 +2614,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2495,21 +2626,21 @@
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,72 +2656,78 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>45800</v>
+        <v>14100</v>
       </c>
       <c r="E58" s="3">
-        <v>15600</v>
+        <v>46100</v>
       </c>
       <c r="F58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>15900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>13200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9600</v>
+        <v>4600</v>
       </c>
       <c r="E59" s="3">
-        <v>8200</v>
+        <v>4600</v>
       </c>
       <c r="F59" s="3">
-        <v>10300</v>
+        <v>7200</v>
       </c>
       <c r="G59" s="3">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="H59" s="3">
-        <v>13500</v>
+        <v>4600</v>
       </c>
       <c r="I59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>2100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>100</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2607,32 +2744,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E60" s="3">
         <v>55400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,32 +2788,35 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>151300</v>
+        <v>168400</v>
       </c>
       <c r="E61" s="3">
-        <v>170200</v>
+        <v>153300</v>
       </c>
       <c r="F61" s="3">
-        <v>126800</v>
+        <v>172200</v>
       </c>
       <c r="G61" s="3">
+        <v>128600</v>
+      </c>
+      <c r="H61" s="3">
         <v>118800</v>
       </c>
-      <c r="H61" s="3">
-        <v>91200</v>
-      </c>
       <c r="I61" s="3">
+        <v>66200</v>
+      </c>
+      <c r="J61" s="3">
         <v>37400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2689,28 +2832,31 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20300</v>
+        <v>15100</v>
       </c>
       <c r="E62" s="3">
-        <v>17400</v>
+        <v>6400</v>
       </c>
       <c r="F62" s="3">
-        <v>17600</v>
+        <v>5700</v>
       </c>
       <c r="G62" s="3">
-        <v>13900</v>
+        <v>6600</v>
       </c>
       <c r="H62" s="3">
-        <v>11800</v>
+        <v>3400</v>
       </c>
       <c r="I62" s="3">
-        <v>700</v>
+        <v>27400</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2730,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,31 +3008,34 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>227100</v>
+        <v>219400</v>
       </c>
       <c r="E66" s="3">
-        <v>211600</v>
+        <v>227000</v>
       </c>
       <c r="F66" s="3">
-        <v>167900</v>
+        <v>211400</v>
       </c>
       <c r="G66" s="3">
-        <v>138500</v>
+        <v>167800</v>
       </c>
       <c r="H66" s="3">
-        <v>117200</v>
+        <v>138200</v>
       </c>
       <c r="I66" s="3">
-        <v>55200</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>116800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>54800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2894,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3028,14 +3196,17 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
+      <c r="N70" s="3">
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,32 +3246,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-34500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-36100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-34700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,32 +3422,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>258000</v>
+      </c>
+      <c r="E76" s="3">
         <v>256800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>165100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>163900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>165800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>160100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35300</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3280,8 +3466,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3510,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,22 +3623,23 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -3457,8 +3656,8 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-66800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-12800</v>
-      </c>
       <c r="H89" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-21000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,8 +3949,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3738,22 +3959,22 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>9600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,31 +4143,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,72 +4317,78 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E100" s="3">
         <v>93500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>37500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="G100" s="3">
-        <v>19200</v>
-      </c>
       <c r="H100" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I100" s="3">
         <v>27900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4150,51 +4399,57 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-71900</v>
+      </c>
+      <c r="E102" s="3">
         <v>25900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -656,211 +656,236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>33200</v>
+      </c>
+      <c r="F8" s="3">
         <v>28100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>29100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>21500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>23700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>21100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>11400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>14900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9900</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F9" s="3">
         <v>2200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1400</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F10" s="3">
         <v>26000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>26300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>18800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>22000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>17800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>10400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>12500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>9700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>8500</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,8 +902,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,8 +948,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,75 +998,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1700</v>
+        <v>4800</v>
       </c>
       <c r="E15" s="3">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="F15" s="3">
         <v>1700</v>
       </c>
       <c r="G15" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="H15" s="3">
         <v>1700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1044,17 +1089,23 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1119,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>40800</v>
+      </c>
+      <c r="F17" s="3">
         <v>21600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>21600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>17700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>20500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>16600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F18" s="3">
         <v>6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>7200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,228 +1239,260 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F20" s="3">
         <v>8800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>6400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>9300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>10400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>7000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>4500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>3700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>6200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>7000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>10700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
+        <v>200</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1535,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>6700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>6800</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>8100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>6800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1685,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1608,14 +1729,20 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1785,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1835,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>8100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>6800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1985,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>8100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>6800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2114,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,38 +2134,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F41" s="3">
         <v>19400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>91300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>65400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>25600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>36600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>19700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,82 +2180,94 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>4000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>26500</v>
+      </c>
+      <c r="F43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>10800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2280,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2121,11 +2312,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2133,14 +2324,20 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2183,38 +2380,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>159600</v>
+      </c>
+      <c r="F46" s="3">
         <v>30800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>101600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>74300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>31800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>39500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>32200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,38 +2430,44 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F47" s="3">
         <v>3000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2900</v>
       </c>
       <c r="G47" s="3">
         <v>2900</v>
       </c>
       <c r="H47" s="3">
-        <v>4100</v>
+        <v>2900</v>
       </c>
       <c r="I47" s="3">
         <v>2900</v>
       </c>
       <c r="J47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L47" s="3">
         <v>2500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2271,38 +2480,44 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F48" s="3">
         <v>2900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,37 +2530,43 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>313400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>318100</v>
+      </c>
+      <c r="F49" s="3">
         <v>164600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>166300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>168300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>169900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>171500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>173200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2359,8 +2580,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2630,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,38 +2680,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>386700</v>
+      </c>
+      <c r="F52" s="3">
         <v>276000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>210200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>128400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>125000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>88700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>68700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>64000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2730,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,38 +2780,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>856500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>874200</v>
+      </c>
+      <c r="F54" s="3">
         <v>477300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>483900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>376700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>331800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>304300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>277300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>90400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2830,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2854,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,8 +2874,10 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2632,21 +2893,21 @@
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,82 +2920,94 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F58" s="3">
         <v>14100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>46100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>15900</v>
       </c>
-      <c r="G58" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7200</v>
       </c>
-      <c r="G59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,38 +3020,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F60" s="3">
         <v>23900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>55400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>23800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>16700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,38 +3070,44 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>242400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>347000</v>
+      </c>
+      <c r="F61" s="3">
         <v>168400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>153300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>172200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>128600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>118800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>66200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>37400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2835,35 +3120,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F62" s="3">
         <v>15100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>6400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>27400</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3170,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3220,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3270,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,38 +3320,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>450900</v>
+      </c>
+      <c r="F66" s="3">
         <v>219400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>227000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>211400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>167800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>138200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>116800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>54800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3370,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3394,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3440,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3490,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3199,14 +3534,20 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,38 +3590,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-39600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-34500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-36100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-34700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-29400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>33600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3640,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3690,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3740,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,38 +3790,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>430700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>424200</v>
+      </c>
+      <c r="F76" s="3">
         <v>258000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>256800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>165100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>163900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>165800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>160100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>35300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3840,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3890,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>8100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>6800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,8 +4019,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3659,17 +4056,23 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +4115,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +4165,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4215,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4265,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4315,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-52300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-66800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="J89" s="3">
         <v>-11900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-21000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-17400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>17100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,8 +4389,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3965,22 +4406,22 @@
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3994,8 +4435,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4485,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4535,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>9600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4609,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4170,11 +4637,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4188,8 +4655,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4705,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4755,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,52 +4805,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>208300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-19200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>93500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>37500</v>
       </c>
-      <c r="G100" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J100" s="3">
         <v>18300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>27900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>8000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>10900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4390,11 +4887,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4402,54 +4899,66 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-88200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>112500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-71900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>25900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>39800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-11100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-10300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>26200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>ABL</t>
   </si>
@@ -656,236 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E8" s="3">
         <v>44100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9900</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2700</v>
       </c>
       <c r="H9" s="3">
         <v>2700</v>
       </c>
       <c r="I9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E10" s="3">
         <v>37000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +917,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,75 +1021,81 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>800</v>
       </c>
       <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>800</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E15" s="3">
         <v>4800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1700</v>
       </c>
       <c r="I15" s="3">
         <v>1700</v>
@@ -1081,7 +1104,7 @@
         <v>1700</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1095,8 +1118,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E17" s="3">
         <v>26700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>21600</v>
       </c>
       <c r="G17" s="3">
         <v>21600</v>
       </c>
       <c r="H17" s="3">
+        <v>21600</v>
+      </c>
+      <c r="I17" s="3">
         <v>17700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E18" s="3">
         <v>17400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,141 +1274,148 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E21" s="3">
         <v>17300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E22" s="3">
         <v>9600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1385,114 +1425,123 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E23" s="3">
         <v>7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E26" s="3">
         <v>5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6800</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E27" s="3">
         <v>4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1735,14 +1796,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,108 +1908,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,41 +2222,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E41" s="3">
         <v>43800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>131900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>91300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>65400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2198,79 +2288,82 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E43" s="3">
         <v>16100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2318,8 +2414,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2330,14 +2426,17 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2386,41 +2485,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E46" s="3">
         <v>61500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>159600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>101600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,22 +2538,25 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E47" s="3">
         <v>12600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2900</v>
       </c>
       <c r="H47" s="3">
         <v>2900</v>
@@ -2460,17 +2565,17 @@
         <v>2900</v>
       </c>
       <c r="J47" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K47" s="3">
         <v>4100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,41 +2591,44 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>400</v>
       </c>
       <c r="K48" s="3">
         <v>400</v>
       </c>
       <c r="L48" s="3">
+        <v>400</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,40 +2644,43 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>310300</v>
+      </c>
+      <c r="E49" s="3">
         <v>313400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>318100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>164600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>166300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>168300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>169900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>171500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>173200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,41 +2803,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>403600</v>
+      </c>
+      <c r="E52" s="3">
         <v>463200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>386700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>276000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>210200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>128400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>125000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>88700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>68700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>64000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,41 +2909,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>848400</v>
+      </c>
+      <c r="E54" s="3">
         <v>856500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>874200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>477300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>483900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>376700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>331800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>304300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>277300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>90400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,8 +3006,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2899,18 +3030,18 @@
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,91 +3057,97 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E58" s="3">
         <v>118600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>38900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>46100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>4600</v>
       </c>
       <c r="G59" s="3">
         <v>4600</v>
       </c>
       <c r="H59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I59" s="3">
         <v>7200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,41 +3163,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E60" s="3">
         <v>130800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,41 +3216,44 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>242900</v>
+      </c>
+      <c r="E61" s="3">
         <v>242400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>347000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>168400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>153300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>172200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>128600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>118800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>66200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3126,38 +3269,41 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24500</v>
+        <v>15300</v>
       </c>
       <c r="E62" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F62" s="3">
         <v>14700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,41 +3481,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>425900</v>
+        <v>426800</v>
       </c>
       <c r="E66" s="3">
+        <v>420900</v>
+      </c>
+      <c r="F66" s="3">
         <v>450900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>219400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>227000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>211400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>167800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>138200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>116800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,16 +3661,19 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -3540,14 +3708,17 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>3</v>
+      <c r="Q70" s="3">
+        <v>0</v>
       </c>
       <c r="R70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,41 +3767,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-53300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-57900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-39600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-34700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,41 +3979,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>416600</v>
+      </c>
+      <c r="E76" s="3">
         <v>430700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>424200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>258000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>256800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>165100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>163900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>165800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>160100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,13 +4219,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -4062,8 +4261,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4270,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-61600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-92000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-52300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-66800</v>
-      </c>
       <c r="H89" s="3">
-        <v>2300</v>
+        <v>-67100</v>
       </c>
       <c r="I89" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J89" s="3">
         <v>-13800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,13 +4611,14 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -4412,19 +4633,19 @@
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>-100</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4441,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-700</v>
-      </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="I94" s="3">
         <v>-300</v>
       </c>
       <c r="J94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K94" s="3">
         <v>9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4643,8 +4877,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,58 +5054,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>208300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>93500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>37500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4893,8 +5142,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4905,60 +5154,66 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-88200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>112500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-71900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
